--- a/media/excel_files/RT-202405.xlsx
+++ b/media/excel_files/RT-202405.xlsx
@@ -413,63 +413,65 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>anno_mes_rt</t>
-        </is>
-      </c>
-      <c r="B1" t="n">
-        <v>202405</v>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>entrega_total</t>
+          <t>anno_mes_rt</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>202405</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>entrega_a_tiempo</t>
+          <t>entrega_total</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>stock_productos</t>
+          <t>entrega_a_tiempo</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pedido_proveedor</t>
+          <t>stock_productos</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>adquisicion_recibida</t>
+          <t>pedido_proveedor</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -479,41 +481,51 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>venta_pedido</t>
+          <t>adquisicion_recibida</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>venta_realizada</t>
+          <t>venta_pedido</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>factura_total</t>
+          <t>venta_realizada</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>factura_pagada</t>
+          <t>factura_total</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>factura_pagada</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
